--- a/templates/Company_Estimate_Template.xlsx
+++ b/templates/Company_Estimate_Template.xlsx
@@ -21028,12 +21028,6 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>1108</v>
-      </c>
       <c r="E18" s="4" t="s">
         <v>1104</v>
       </c>
@@ -21220,14 +21214,6 @@
         <v>274</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="4" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
     <row r="42" spans="1:2">
       <c r="A42" s="4" t="s">
         <v>870</v>
@@ -21444,14 +21430,6 @@
         <v>320</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="4" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>508</v>
-      </c>
-    </row>
     <row r="70" spans="1:2">
       <c r="A70" s="4" t="s">
         <v>901</v>
@@ -21692,14 +21670,6 @@
         <v>940</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="4" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>1112</v>
-      </c>
-    </row>
     <row r="101" spans="1:2">
       <c r="A101" s="4" t="s">
         <v>941</v>
@@ -21940,14 +21910,6 @@
         <v>435</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>1114</v>
-      </c>
-    </row>
     <row r="132" spans="1:2">
       <c r="A132" s="4" t="s">
         <v>976</v>
@@ -22220,14 +22182,6 @@
         <v>478</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="4" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>998</v>
-      </c>
-    </row>
     <row r="167" spans="1:2">
       <c r="A167" s="4" t="s">
         <v>1013</v>
@@ -22682,14 +22636,6 @@
       </c>
       <c r="B223" s="4" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="4" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="225" spans="1:2">
